--- a/data/trans_orig/IMC_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2007</t>
+          <t>Población con sobrepeso u obesidad en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139799</t>
+          <t>138018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171387</t>
+          <t>169825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118578</t>
+          <t>117340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232249</t>
+          <t>231057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279803</t>
+          <t>278894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97120</t>
+          <t>98682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128708</t>
+          <t>130489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141033</t>
+          <t>142271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174919</t>
+          <t>174918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248314</t>
+          <t>249223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295868</t>
+          <t>297060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228471</t>
+          <t>228678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270588</t>
+          <t>273568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>217331</t>
+          <t>219871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>261592</t>
+          <t>262301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>456795</t>
+          <t>456492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>522278</t>
+          <t>520391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217957</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260074</t>
+          <t>259867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229149</t>
+          <t>228440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273410</t>
+          <t>270870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457008</t>
+          <t>458895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522491</t>
+          <t>522794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156461</t>
+          <t>158484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193447</t>
+          <t>193908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156485</t>
+          <t>154860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192399</t>
+          <t>192301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324782</t>
+          <t>324163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375182</t>
+          <t>375382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>124938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162385</t>
+          <t>160362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141852</t>
+          <t>141950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177766</t>
+          <t>179391</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277915</t>
+          <t>277715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328315</t>
+          <t>328934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220431</t>
+          <t>221624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255929</t>
+          <t>258410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161771</t>
+          <t>160779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>197613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>392142</t>
+          <t>392044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>442508</t>
+          <t>444226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101216</t>
+          <t>98735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136714</t>
+          <t>135521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172571</t>
+          <t>172903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208745</t>
+          <t>209737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285154</t>
+          <t>283436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335520</t>
+          <t>335618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115998</t>
+          <t>116731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142487</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89145</t>
+          <t>90867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>120732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214143</t>
+          <t>214679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255916</t>
+          <t>256970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58477</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>81751</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113338</t>
+          <t>111616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147531</t>
+          <t>146477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189304</t>
+          <t>188768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149142</t>
+          <t>147612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179940</t>
+          <t>179070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123859</t>
+          <t>125411</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157285</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285561</t>
+          <t>281181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>328801</t>
+          <t>327440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88811</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119609</t>
+          <t>121139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117817</t>
+          <t>117077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>149691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215052</t>
+          <t>216413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258292</t>
+          <t>262672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>347734</t>
+          <t>348867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>396711</t>
+          <t>397068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280323</t>
+          <t>279620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>330374</t>
+          <t>330022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>641443</t>
+          <t>639550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712525</t>
+          <t>715734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217366</t>
+          <t>217009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>266343</t>
+          <t>265210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304814</t>
+          <t>305166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>354865</t>
+          <t>355568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>536740</t>
+          <t>533531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>607822</t>
+          <t>609715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>411973</t>
+          <t>410232</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>467615</t>
+          <t>464233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>299763</t>
+          <t>305167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>361329</t>
+          <t>358053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>728703</t>
+          <t>730260</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>807873</t>
+          <t>806959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>259629</t>
+          <t>263011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>317012</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>403758</t>
+          <t>407034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>465324</t>
+          <t>459920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684458</t>
+          <t>685372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>763628</t>
+          <t>762071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1870667</t>
+          <t>1866586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1980387</t>
+          <t>1979827</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1514167</t>
+          <t>1515368</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1636648</t>
+          <t>1632779</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3408281</t>
+          <t>3418548</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3574539</t>
+          <t>3579984</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1263692</t>
+          <t>1264252</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1373412</t>
+          <t>1377493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1696330</t>
+          <t>1700199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1818811</t>
+          <t>1817610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3002518</t>
+          <t>2997073</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3168776</t>
+          <t>3158509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2012</t>
+          <t>Población con sobrepeso u obesidad en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167309</t>
+          <t>168598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201305</t>
+          <t>201963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122754</t>
+          <t>122692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158073</t>
+          <t>157296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302024</t>
+          <t>304198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349524</t>
+          <t>350430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84095</t>
+          <t>83437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>116802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110061</t>
+          <t>110838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>145442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204009</t>
+          <t>203103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251509</t>
+          <t>249335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248222</t>
+          <t>246785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293291</t>
+          <t>293753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270052</t>
+          <t>269446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314845</t>
+          <t>314638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>529813</t>
+          <t>529396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>593344</t>
+          <t>595135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202996</t>
+          <t>202534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248065</t>
+          <t>249502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179637</t>
+          <t>179844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224430</t>
+          <t>225036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397425</t>
+          <t>395634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>460956</t>
+          <t>461373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215393</t>
+          <t>216613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248407</t>
+          <t>248062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163762</t>
+          <t>163060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201295</t>
+          <t>200732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390282</t>
+          <t>388678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>440113</t>
+          <t>441547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74709</t>
+          <t>75054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107723</t>
+          <t>106503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137784</t>
+          <t>138347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175317</t>
+          <t>176019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222082</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271913</t>
+          <t>273517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232071</t>
+          <t>233771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269655</t>
+          <t>270990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172567</t>
+          <t>172509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210278</t>
+          <t>208956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416780</t>
+          <t>415517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467821</t>
+          <t>469351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90322</t>
+          <t>88987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127906</t>
+          <t>126206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140512</t>
+          <t>141834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178223</t>
+          <t>178281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>242947</t>
+          <t>241417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293988</t>
+          <t>295251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117995</t>
+          <t>118370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147351</t>
+          <t>146987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>84962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115906</t>
+          <t>114228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209760</t>
+          <t>213129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252299</t>
+          <t>253823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64098</t>
+          <t>64462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93454</t>
+          <t>93079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91918</t>
+          <t>93596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121891</t>
+          <t>122862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>166974</t>
+          <t>165450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209513</t>
+          <t>206144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>192149</t>
+          <t>190743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>219844</t>
+          <t>220714</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>148953</t>
+          <t>151114</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183953</t>
+          <t>184064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>352405</t>
+          <t>351311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>397153</t>
+          <t>397566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81832</t>
+          <t>83238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>93884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154776</t>
+          <t>154363</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199524</t>
+          <t>200618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>407433</t>
+          <t>408483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>458358</t>
+          <t>458414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>357734</t>
+          <t>356611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>412413</t>
+          <t>411707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>782568</t>
+          <t>777300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>856117</t>
+          <t>853545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203361</t>
+          <t>203305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254286</t>
+          <t>253236</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277012</t>
+          <t>277718</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331691</t>
+          <t>332814</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>495027</t>
+          <t>497599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>568576</t>
+          <t>573844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>459644</t>
+          <t>457241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>512901</t>
+          <t>513071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>362407</t>
+          <t>361016</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>418870</t>
+          <t>418575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>834117</t>
+          <t>831056</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>915601</t>
+          <t>913145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235509</t>
+          <t>235339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>288766</t>
+          <t>291169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>360991</t>
+          <t>361286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>417454</t>
+          <t>418845</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>612670</t>
+          <t>615126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694154</t>
+          <t>697215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2139359</t>
+          <t>2139579</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2254473</t>
+          <t>2253686</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1791319</t>
+          <t>1790187</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1908600</t>
+          <t>1912198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3964416</t>
+          <t>3972883</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4131460</t>
+          <t>4136184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1105867</t>
+          <t>1106654</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1220981</t>
+          <t>1220761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1498942</t>
+          <t>1495344</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1616223</t>
+          <t>1617355</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2636422</t>
+          <t>2631698</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2803466</t>
+          <t>2794999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2016</t>
+          <t>Población con sobrepeso u obesidad en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142958</t>
+          <t>141812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177215</t>
+          <t>178127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110642</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144462</t>
+          <t>145960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263088</t>
+          <t>264926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314576</t>
+          <t>313110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108654</t>
+          <t>107742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142911</t>
+          <t>144057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123126</t>
+          <t>121628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156946</t>
+          <t>155489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238881</t>
+          <t>240347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290369</t>
+          <t>288531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>277549</t>
+          <t>275924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>322801</t>
+          <t>323559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,47 +7737,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>279856</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>256207</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>301058</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>55,98%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>279856</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>257912</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>305065</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>548411</t>
+          <t>549327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>612932</t>
+          <t>613367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>172272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218282</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,47 +7850,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>220105</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>198903</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>243754</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>44,02%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220105</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>194896</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>242049</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>382860</t>
+          <t>382425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447381</t>
+          <t>446465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>179864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211849</t>
+          <t>212505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157641</t>
+          <t>157288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193422</t>
+          <t>193983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349749</t>
+          <t>347159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397393</t>
+          <t>395759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103289</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133900</t>
+          <t>135274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>132940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169282</t>
+          <t>169635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244668</t>
+          <t>246302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292312</t>
+          <t>294902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194608</t>
+          <t>193702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231350</t>
+          <t>231612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154113</t>
+          <t>151987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193401</t>
+          <t>191559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359824</t>
+          <t>359869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411384</t>
+          <t>409877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123793</t>
+          <t>123531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160535</t>
+          <t>161441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143302</t>
+          <t>145144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182590</t>
+          <t>184716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280462</t>
+          <t>281969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332022</t>
+          <t>331977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107909</t>
+          <t>107706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137096</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133578</t>
+          <t>132010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159601</t>
+          <t>158374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>247143</t>
+          <t>249622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285153</t>
+          <t>286991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69489</t>
+          <t>71133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98676</t>
+          <t>98879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56941</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82964</t>
+          <t>84532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137974</t>
+          <t>136136</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175984</t>
+          <t>173505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147275</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177048</t>
+          <t>178284</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>123145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153002</t>
+          <t>155825</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>278487</t>
+          <t>277759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>324301</t>
+          <t>322934</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115848</t>
+          <t>116304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116212</t>
+          <t>113389</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148864</t>
+          <t>146069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208036</t>
+          <t>209403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253850</t>
+          <t>254578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>330590</t>
+          <t>331233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>381293</t>
+          <t>383386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246812</t>
+          <t>247033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300738</t>
+          <t>296704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589504</t>
+          <t>593550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>664471</t>
+          <t>663561</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232412</t>
+          <t>230319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>283115</t>
+          <t>282472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343471</t>
+          <t>347505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397397</t>
+          <t>397176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>593444</t>
+          <t>594354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>668411</t>
+          <t>664365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>445426</t>
+          <t>446349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>501151</t>
+          <t>501918</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>408094</t>
+          <t>405668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>464013</t>
+          <t>460474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>869486</t>
+          <t>870091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>947480</t>
+          <t>950894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>237371</t>
+          <t>236604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>293096</t>
+          <t>292173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>317175</t>
+          <t>320714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>373094</t>
+          <t>375520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>572230</t>
+          <t>568816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>650224</t>
+          <t>649619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1935748</t>
+          <t>1932044</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2047170</t>
+          <t>2043113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1690039</t>
+          <t>1687084</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1806197</t>
+          <t>1809568</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3656367</t>
+          <t>3644058</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3817441</t>
+          <t>3813354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1226746</t>
+          <t>1230803</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1338168</t>
+          <t>1341872</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1536131</t>
+          <t>1532760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1652289</t>
+          <t>1655244</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2798803</t>
+          <t>2802890</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2959877</t>
+          <t>2972186</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2023</t>
+          <t>Población con sobrepeso u obesidad en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174879</t>
+          <t>177287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>219790</t>
+          <t>219037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124598</t>
+          <t>124579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152907</t>
+          <t>153250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308445</t>
+          <t>313040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>360823</t>
+          <t>364437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>92406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136564</t>
+          <t>134156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134565</t>
+          <t>134222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162874</t>
+          <t>162893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238092</t>
+          <t>234478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290470</t>
+          <t>285875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>308062</t>
+          <t>308672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365091</t>
+          <t>366063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231492</t>
+          <t>231890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272090</t>
+          <t>271284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>553922</t>
+          <t>551425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622323</t>
+          <t>626862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148051</t>
+          <t>147079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205080</t>
+          <t>204470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222742</t>
+          <t>223548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263340</t>
+          <t>262942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385651</t>
+          <t>381112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454052</t>
+          <t>456549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185127</t>
+          <t>184690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221843</t>
+          <t>220194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178780</t>
+          <t>179074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212356</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375437</t>
+          <t>376490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>423811</t>
+          <t>421264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87975</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124691</t>
+          <t>125128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>125311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157626</t>
+          <t>157332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222413</t>
+          <t>224960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270787</t>
+          <t>269734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169713</t>
+          <t>168481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207943</t>
+          <t>208843</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187006</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>305186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>375443</t>
+          <t>377559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493415</t>
+          <t>502731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78050</t>
+          <t>77150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116280</t>
+          <t>117512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91537</t>
+          <t>90806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208986</t>
+          <t>211337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188570</t>
+          <t>179254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306542</t>
+          <t>304426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84808</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106871</t>
+          <t>107305</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102546</t>
+          <t>103145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123158</t>
+          <t>123283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193680</t>
+          <t>193348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223738</t>
+          <t>222231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>70761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93258</t>
+          <t>94187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83550</t>
+          <t>83425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>103563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>161036</t>
+          <t>162543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191094</t>
+          <t>191426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>169900</t>
+          <t>170060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>198622</t>
+          <t>199761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104611</t>
+          <t>105452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129539</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283492</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320259</t>
+          <t>322185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69067</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97789</t>
+          <t>97629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119752</t>
+          <t>119604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144680</t>
+          <t>143839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196720</t>
+          <t>194794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>233487</t>
+          <t>235354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>329143</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>392307</t>
+          <t>392330</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>378067</t>
+          <t>378422</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>657749</t>
+          <t>663833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>748328</t>
+          <t>754087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1057652</t>
+          <t>1062577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221873</t>
+          <t>221850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>282810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169763</t>
+          <t>163679</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>449445</t>
+          <t>449090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384040</t>
+          <t>379115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>693364</t>
+          <t>687605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521850</t>
+          <t>523407</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>793988</t>
+          <t>775190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>361963</t>
+          <t>362211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>408521</t>
+          <t>409217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>903368</t>
+          <t>903931</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1265604</t>
+          <t>1284200</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123919</t>
+          <t>142717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>396057</t>
+          <t>394500</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>293443</t>
+          <t>292747</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>340001</t>
+          <t>339753</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>354268</t>
+          <t>335672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>716504</t>
+          <t>715941</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2087287</t>
+          <t>2088119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2493642</t>
+          <t>2474728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1795803</t>
+          <t>1806140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2223087</t>
+          <t>2215162</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3939613</t>
+          <t>3946098</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4497479</t>
+          <t>4540917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>904596</t>
+          <t>923510</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1310951</t>
+          <t>1310119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1277091</t>
+          <t>1285016</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1704375</t>
+          <t>1694038</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2400937</t>
+          <t>2357499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2958803</t>
+          <t>2952318</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138018</t>
+          <t>139110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169825</t>
+          <t>170129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117340</t>
+          <t>118503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231057</t>
+          <t>231124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>276562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98682</t>
+          <t>98378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130489</t>
+          <t>129397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142271</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174918</t>
+          <t>174869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249223</t>
+          <t>251555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297060</t>
+          <t>296993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228678</t>
+          <t>225010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273568</t>
+          <t>270898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219871</t>
+          <t>218597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262301</t>
+          <t>260753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>456492</t>
+          <t>458623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>520391</t>
+          <t>520947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214977</t>
+          <t>217647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>259867</t>
+          <t>263535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228440</t>
+          <t>229988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>270870</t>
+          <t>272144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>458895</t>
+          <t>458339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522794</t>
+          <t>520663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158484</t>
+          <t>158471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193908</t>
+          <t>192786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154860</t>
+          <t>156065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192301</t>
+          <t>192564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324163</t>
+          <t>321093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375382</t>
+          <t>374156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124938</t>
+          <t>126060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160362</t>
+          <t>160375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141950</t>
+          <t>141687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179391</t>
+          <t>178186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277715</t>
+          <t>278941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328934</t>
+          <t>332004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221624</t>
+          <t>221288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258410</t>
+          <t>255695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160779</t>
+          <t>162193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197613</t>
+          <t>198882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>392044</t>
+          <t>393606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444226</t>
+          <t>444761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98735</t>
+          <t>101450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135521</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172903</t>
+          <t>171634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209737</t>
+          <t>208323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283436</t>
+          <t>282901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335618</t>
+          <t>334056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116731</t>
+          <t>117501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>143219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>90876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120732</t>
+          <t>118992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214679</t>
+          <t>214499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256970</t>
+          <t>253619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>83463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81751</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111616</t>
+          <t>111607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146477</t>
+          <t>149828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188768</t>
+          <t>188948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147612</t>
+          <t>147586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179070</t>
+          <t>179099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125411</t>
+          <t>125220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>159045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281181</t>
+          <t>282915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327440</t>
+          <t>328910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121139</t>
+          <t>121165</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117077</t>
+          <t>116057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149691</t>
+          <t>149882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216413</t>
+          <t>214943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262672</t>
+          <t>260938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>348867</t>
+          <t>345857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>397068</t>
+          <t>395896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>279620</t>
+          <t>276431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>330022</t>
+          <t>330545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>639550</t>
+          <t>639553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>715734</t>
+          <t>713717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217009</t>
+          <t>218181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>265210</t>
+          <t>268220</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305166</t>
+          <t>304643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355568</t>
+          <t>358757</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>533531</t>
+          <t>535548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609715</t>
+          <t>609712</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>410232</t>
+          <t>412564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464233</t>
+          <t>463457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>305167</t>
+          <t>302289</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358053</t>
+          <t>358242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>730260</t>
+          <t>731935</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>806959</t>
+          <t>811353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>263011</t>
+          <t>263787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>317012</t>
+          <t>314680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>407034</t>
+          <t>406845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>459920</t>
+          <t>462798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>685372</t>
+          <t>680978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762071</t>
+          <t>760396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1866586</t>
+          <t>1869898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1979827</t>
+          <t>1981608</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1515368</t>
+          <t>1519462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1632779</t>
+          <t>1631473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3418548</t>
+          <t>3422415</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3579984</t>
+          <t>3589263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1264252</t>
+          <t>1262471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1377493</t>
+          <t>1374181</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1700199</t>
+          <t>1701505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1817610</t>
+          <t>1813516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2997073</t>
+          <t>2987794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3158509</t>
+          <t>3154642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168598</t>
+          <t>168516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201963</t>
+          <t>201182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122692</t>
+          <t>122743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157296</t>
+          <t>157338</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>302240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>350430</t>
+          <t>351148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83437</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116802</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110838</t>
+          <t>110796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145442</t>
+          <t>145391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203103</t>
+          <t>202385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249335</t>
+          <t>251293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246785</t>
+          <t>246983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293753</t>
+          <t>293592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269446</t>
+          <t>267049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314638</t>
+          <t>314378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>529396</t>
+          <t>533119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595135</t>
+          <t>596160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202534</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249502</t>
+          <t>249304</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179844</t>
+          <t>180104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225036</t>
+          <t>227433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395634</t>
+          <t>394609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461373</t>
+          <t>457650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>216613</t>
+          <t>215469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248062</t>
+          <t>249721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163060</t>
+          <t>162818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200732</t>
+          <t>201659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>388678</t>
+          <t>390132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>441547</t>
+          <t>439765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>73395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106503</t>
+          <t>107647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138347</t>
+          <t>137420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176019</t>
+          <t>176261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>222430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273517</t>
+          <t>272063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233771</t>
+          <t>233308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>270990</t>
+          <t>270001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172509</t>
+          <t>172731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208956</t>
+          <t>210579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>415517</t>
+          <t>419642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>469351</t>
+          <t>469134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88987</t>
+          <t>89976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>126669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141834</t>
+          <t>140211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178281</t>
+          <t>178059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241417</t>
+          <t>241634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295251</t>
+          <t>291126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118370</t>
+          <t>118127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146987</t>
+          <t>146556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84962</t>
+          <t>83694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114228</t>
+          <t>113036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213129</t>
+          <t>211046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253823</t>
+          <t>253668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>64893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93079</t>
+          <t>93322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93596</t>
+          <t>94788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>122862</t>
+          <t>124130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165450</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206144</t>
+          <t>208227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190743</t>
+          <t>191758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220714</t>
+          <t>220392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>151114</t>
+          <t>151814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>184064</t>
+          <t>183241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>351311</t>
+          <t>351600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>397566</t>
+          <t>395831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53267</t>
+          <t>53589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83238</t>
+          <t>82223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93884</t>
+          <t>94707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126834</t>
+          <t>126134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154363</t>
+          <t>156098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200618</t>
+          <t>200329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>408483</t>
+          <t>407171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>458414</t>
+          <t>459311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>356611</t>
+          <t>352658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>411707</t>
+          <t>408412</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>777300</t>
+          <t>780628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>853545</t>
+          <t>855589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203305</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253236</t>
+          <t>254548</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277718</t>
+          <t>281013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332814</t>
+          <t>336767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>497599</t>
+          <t>495555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573844</t>
+          <t>570516</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>457241</t>
+          <t>457019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>513071</t>
+          <t>512201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>361016</t>
+          <t>362647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>418575</t>
+          <t>417799</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>831056</t>
+          <t>832106</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>913145</t>
+          <t>912484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235339</t>
+          <t>236209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>291169</t>
+          <t>291391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>361286</t>
+          <t>362062</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>418845</t>
+          <t>417214</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>615126</t>
+          <t>615787</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>697215</t>
+          <t>696165</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2139579</t>
+          <t>2142227</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2253686</t>
+          <t>2257017</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1790187</t>
+          <t>1792324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1912198</t>
+          <t>1914143</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3972883</t>
+          <t>3960643</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4136184</t>
+          <t>4128547</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1106654</t>
+          <t>1103323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1220761</t>
+          <t>1218113</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1495344</t>
+          <t>1493399</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1617355</t>
+          <t>1615218</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2631698</t>
+          <t>2639335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2794999</t>
+          <t>2807239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141812</t>
+          <t>141173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178127</t>
+          <t>177075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112099</t>
+          <t>110542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145960</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264926</t>
+          <t>261108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>313110</t>
+          <t>311108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107742</t>
+          <t>108794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144057</t>
+          <t>144696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121628</t>
+          <t>123363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155489</t>
+          <t>157046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240347</t>
+          <t>242349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288531</t>
+          <t>292349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275924</t>
+          <t>280944</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>323559</t>
+          <t>323025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256207</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301058</t>
+          <t>302367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549327</t>
+          <t>551404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>613367</t>
+          <t>611184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172272</t>
+          <t>172806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219907</t>
+          <t>214887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198903</t>
+          <t>197594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243754</t>
+          <t>244473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>382425</t>
+          <t>384608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446465</t>
+          <t>444388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179864</t>
+          <t>179336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212505</t>
+          <t>212910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157288</t>
+          <t>157257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193983</t>
+          <t>193072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347159</t>
+          <t>348539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>395759</t>
+          <t>396147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102633</t>
+          <t>102228</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135274</t>
+          <t>135802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132940</t>
+          <t>133851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>169635</t>
+          <t>169666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246302</t>
+          <t>245914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294902</t>
+          <t>293522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193702</t>
+          <t>194360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231612</t>
+          <t>232101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151987</t>
+          <t>153602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191559</t>
+          <t>191687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359869</t>
+          <t>359926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409877</t>
+          <t>413472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123531</t>
+          <t>123042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>160783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145144</t>
+          <t>145016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184716</t>
+          <t>183101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281969</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331977</t>
+          <t>331920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107706</t>
+          <t>107115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135452</t>
+          <t>134487</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132010</t>
+          <t>132290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158374</t>
+          <t>158626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>249622</t>
+          <t>248550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286991</t>
+          <t>287326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>72098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98879</t>
+          <t>99470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84532</t>
+          <t>84252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136136</t>
+          <t>135801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173505</t>
+          <t>174577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146819</t>
+          <t>146688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178284</t>
+          <t>179356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123145</t>
+          <t>119781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>155825</t>
+          <t>154919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277759</t>
+          <t>276832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322934</t>
+          <t>324107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>83767</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116304</t>
+          <t>116435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113389</t>
+          <t>114295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>149433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209403</t>
+          <t>208230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254578</t>
+          <t>255505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>331233</t>
+          <t>331654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>383386</t>
+          <t>382899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>247033</t>
+          <t>246332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>296704</t>
+          <t>297698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>593550</t>
+          <t>588645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>663561</t>
+          <t>664391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230319</t>
+          <t>230806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282472</t>
+          <t>282051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>347505</t>
+          <t>346511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397176</t>
+          <t>397877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>594354</t>
+          <t>593524</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>664365</t>
+          <t>669270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>446349</t>
+          <t>445765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>501918</t>
+          <t>498358</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>405668</t>
+          <t>404692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>460474</t>
+          <t>461444</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>870091</t>
+          <t>866960</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>950894</t>
+          <t>948329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236604</t>
+          <t>240164</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>292173</t>
+          <t>292757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>320714</t>
+          <t>319744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>375520</t>
+          <t>376496</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>568816</t>
+          <t>571381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>649619</t>
+          <t>652750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1932044</t>
+          <t>1929506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2043113</t>
+          <t>2045342</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1687084</t>
+          <t>1687468</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1809568</t>
+          <t>1800615</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3644058</t>
+          <t>3651727</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3813354</t>
+          <t>3812538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1230803</t>
+          <t>1228574</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1341872</t>
+          <t>1344410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1532760</t>
+          <t>1541713</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1655244</t>
+          <t>1654860</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2802890</t>
+          <t>2803706</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2972186</t>
+          <t>2964517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>198421</t>
+          <t>202332</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177287</t>
+          <t>184233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>219037</t>
+          <t>220138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>139187</t>
+          <t>156079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124579</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153250</t>
+          <t>169944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>337608</t>
+          <t>358412</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313040</t>
+          <t>333211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>364437</t>
+          <t>380405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>113022</t>
+          <t>116513</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>98707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134156</t>
+          <t>134612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>148285</t>
+          <t>157731</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134222</t>
+          <t>143866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162893</t>
+          <t>172943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>261307</t>
+          <t>274243</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234478</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285875</t>
+          <t>299444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287472</t>
+          <t>313810</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287472</t>
+          <t>313810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287472</t>
+          <t>313810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>598915</t>
+          <t>632655</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>598915</t>
+          <t>632655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>598915</t>
+          <t>632655</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>337805</t>
+          <t>347712</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>308672</t>
+          <t>321096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366063</t>
+          <t>375154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>250802</t>
+          <t>266008</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231890</t>
+          <t>244806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271284</t>
+          <t>286872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>588608</t>
+          <t>613720</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551425</t>
+          <t>576123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>626862</t>
+          <t>650494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>175337</t>
+          <t>177474</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147079</t>
+          <t>150032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204470</t>
+          <t>204090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>244030</t>
+          <t>258531</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223548</t>
+          <t>237667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262942</t>
+          <t>279733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>419366</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>381112</t>
+          <t>399231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456549</t>
+          <t>473602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513142</t>
+          <t>525186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513142</t>
+          <t>525186</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513142</t>
+          <t>525186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>494832</t>
+          <t>524539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>494832</t>
+          <t>524539</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>494832</t>
+          <t>524539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1007974</t>
+          <t>1049725</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1007974</t>
+          <t>1049725</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1007974</t>
+          <t>1049725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>203841</t>
+          <t>204907</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184690</t>
+          <t>187717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220194</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>195421</t>
+          <t>201682</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179074</t>
+          <t>186450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>217401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>399262</t>
+          <t>406589</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376490</t>
+          <t>382124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421264</t>
+          <t>429463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>105977</t>
+          <t>103537</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>87652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125128</t>
+          <t>120727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140985</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125311</t>
+          <t>125389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157332</t>
+          <t>156340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>246962</t>
+          <t>244645</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224960</t>
+          <t>221771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269734</t>
+          <t>269110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>309818</t>
+          <t>308444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>309818</t>
+          <t>308444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>309818</t>
+          <t>308444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>336406</t>
+          <t>342790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>336406</t>
+          <t>342790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336406</t>
+          <t>342790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>646224</t>
+          <t>651234</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>646224</t>
+          <t>651234</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>646224</t>
+          <t>651234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>189472</t>
+          <t>215962</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168481</t>
+          <t>190423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208843</t>
+          <t>238004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>228342</t>
+          <t>179994</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>184655</t>
+          <t>159763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305186</t>
+          <t>197678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>417814</t>
+          <t>395955</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>377559</t>
+          <t>363408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>502731</t>
+          <t>423548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96521</t>
+          <t>117783</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77150</t>
+          <t>95741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117512</t>
+          <t>143322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167650</t>
+          <t>187738</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90806</t>
+          <t>170054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211337</t>
+          <t>207969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>264171</t>
+          <t>305522</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179254</t>
+          <t>277929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304426</t>
+          <t>338069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>285993</t>
+          <t>333745</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>285993</t>
+          <t>333745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>285993</t>
+          <t>333745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>395992</t>
+          <t>367732</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>395992</t>
+          <t>367732</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>395992</t>
+          <t>367732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>681985</t>
+          <t>701477</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>681985</t>
+          <t>701477</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>681985</t>
+          <t>701477</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>106757</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>95005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>120691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>112311</t>
+          <t>120939</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103145</t>
+          <t>109367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123283</t>
+          <t>132337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>208180</t>
+          <t>227696</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>212502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222231</t>
+          <t>245948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82197</t>
+          <t>98173</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70761</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>109925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94397</t>
+          <t>105452</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83425</t>
+          <t>94054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103563</t>
+          <t>117024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>203625</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162543</t>
+          <t>185373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191426</t>
+          <t>218819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206708</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384774</t>
+          <t>431321</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384774</t>
+          <t>431321</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384774</t>
+          <t>431321</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>183524</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170060</t>
+          <t>168363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>199761</t>
+          <t>198137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>117507</t>
+          <t>123912</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105452</t>
+          <t>112207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129687</t>
+          <t>137064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>302806</t>
+          <t>307436</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281625</t>
+          <t>286806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322185</t>
+          <t>326521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>85288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>70675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97629</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>131784</t>
+          <t>131971</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119604</t>
+          <t>118819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143839</t>
+          <t>143676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214173</t>
+          <t>217259</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194794</t>
+          <t>198174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>235354</t>
+          <t>237889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>267689</t>
+          <t>268812</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>267689</t>
+          <t>268812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>267689</t>
+          <t>268812</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>249291</t>
+          <t>255883</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>249291</t>
+          <t>255883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>249291</t>
+          <t>255883</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>516979</t>
+          <t>524695</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>516979</t>
+          <t>524695</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>516979</t>
+          <t>524695</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>362703</t>
+          <t>430357</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>331370</t>
+          <t>399088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>392330</t>
+          <t>460940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>498109</t>
+          <t>357339</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>378422</t>
+          <t>333460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>663833</t>
+          <t>383780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>860811</t>
+          <t>787696</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>754087</t>
+          <t>745018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1062577</t>
+          <t>828424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>56,96%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>251477</t>
+          <t>276214</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221850</t>
+          <t>245631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282810</t>
+          <t>307483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>329403</t>
+          <t>390597</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>163679</t>
+          <t>364156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>449090</t>
+          <t>414476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>580881</t>
+          <t>666811</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>379115</t>
+          <t>626083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>687605</t>
+          <t>709489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>614180</t>
+          <t>706571</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>614180</t>
+          <t>706571</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>614180</t>
+          <t>706571</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>827512</t>
+          <t>747936</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>827512</t>
+          <t>747936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>827512</t>
+          <t>747936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1454507</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1454507</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1454507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>634673</t>
+          <t>446820</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>523407</t>
+          <t>416704</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>775190</t>
+          <t>476209</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>387339</t>
+          <t>448302</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>362211</t>
+          <t>422073</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>409217</t>
+          <t>471843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1022012</t>
+          <t>895122</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>903931</t>
+          <t>852104</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1284200</t>
+          <t>933949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>283234</t>
+          <t>338963</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142717</t>
+          <t>309574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>394500</t>
+          <t>369079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>314625</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>292747</t>
+          <t>341362</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339753</t>
+          <t>391132</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>597860</t>
+          <t>703865</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>335672</t>
+          <t>665038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>715941</t>
+          <t>746883</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>917907</t>
+          <t>785783</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>917907</t>
+          <t>785783</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>917907</t>
+          <t>785783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>701964</t>
+          <t>813205</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>701964</t>
+          <t>813205</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>701964</t>
+          <t>813205</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1619872</t>
+          <t>1598987</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1619872</t>
+          <t>1598987</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1619872</t>
+          <t>1598987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2088119</t>
+          <t>2075818</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2474728</t>
+          <t>2201794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1806140</t>
+          <t>1798777</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2215162</t>
+          <t>1905633</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3946098</t>
+          <t>3911796</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4540917</t>
+          <t>4078433</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1190155</t>
+          <t>1313944</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>923510</t>
+          <t>1250521</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1310119</t>
+          <t>1376497</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1571159</t>
+          <t>1738031</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1285016</t>
+          <t>1686653</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1694038</t>
+          <t>1793509</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2761314</t>
+          <t>3051975</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2357499</t>
+          <t>2966168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2952318</t>
+          <t>3132805</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3398238</t>
+          <t>3452315</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3500178</t>
+          <t>3592286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6898416</t>
+          <t>7044601</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
